--- a/output/2026-10-06_06_Croazia_Grad_Zagreb_Componentistica_Ventilazione_industriale.xlsx
+++ b/output/2026-10-06_06_Croazia_Grad_Zagreb_Componentistica_Ventilazione_industriale.xlsx
@@ -494,10 +494,9 @@
           <t>+385 1 3818 004</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Distributore pneumatica/oleodinamica/meccatronica; Premium Partner Filtration Group Industrial per filtrazione aria industriale (confermato su industrial.filtrationgroup.com). Vero distributore terzo, non produttore.</t>
+          <t>Distributore pneumatica/oleodinamica/meccatronica; Premium Partner Filtration Group Industrial per filtrazione aria industriale (confermato su industrial.filtrationgroup.com). Vero distributore terzo, non produttore. [DUPLICATO — vedi anche: 2026-10-05_20_Croazia_Međimurska_Impiantistica_aspirazione_industriale.xlsx]</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -539,7 +538,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Produzione/distribuzione filtri aria industriale e HVAC, anche di marchi terzi europei. ISO 9001/14001/45001.</t>
+          <t>Produzione/distribuzione filtri aria industriale e HVAC, anche di marchi terzi europei. ISO 9001/14001/45001. [DUPLICATO — vedi anche: 2026-09-07_19_Croazia_Zagrebacka_Depolverazione_Trattamento_aria.xlsx]</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -554,7 +553,6 @@
           <t>INVENTO ventilacija d.o.o.</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr"/>
       <c r="C4" t="inlineStr">
         <is>
           <t>Grad Zagreb</t>
@@ -619,7 +617,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Distribuzione attrezzature saldatura incl. impianti aspirazione fumi/polveri di saldatura (catalogo include esplicitamente welding fume and dust filtration equipment).</t>
+          <t>Distribuzione attrezzature saldatura incl. impianti aspirazione fumi/polveri di saldatura (catalogo include esplicitamente welding fume and dust filtration equipment). [DUPLICATO — vedi anche: 2026-10-06_05_Croazia_Grad_Zagreb_Impiantistica_aspirazione_industriale.xlsx]</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -634,7 +632,6 @@
           <t>TERMO-ODRŽAVANJA d.o.o.</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr"/>
       <c r="C6" t="inlineStr">
         <is>
           <t>Grad Zagreb</t>

--- a/output/2026-10-06_06_Croazia_Grad_Zagreb_Componentistica_Ventilazione_industriale.xlsx
+++ b/output/2026-10-06_06_Croazia_Grad_Zagreb_Componentistica_Ventilazione_industriale.xlsx
@@ -580,7 +580,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (12/10/2026)</t>
         </is>
       </c>
     </row>
@@ -659,7 +659,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (12/10/2026)</t>
         </is>
       </c>
     </row>
